--- a/Mentor 1.xlsx
+++ b/Mentor 1.xlsx
@@ -418,7 +418,7 @@
         <v>Mentor 1</v>
       </c>
       <c r="C2" t="str">
-        <v>https://leetcode.com/u/CC1IK8Szok/</v>
+        <v>https://leetcode.com/u/MONTI_07/</v>
       </c>
     </row>
     <row r="3">

--- a/Mentor 1.xlsx
+++ b/Mentor 1.xlsx
@@ -451,7 +451,7 @@
         <v>Mentor 1</v>
       </c>
       <c r="C5" t="str">
-        <v>https://leetcode.com/u/dFMbl0rCYX/</v>
+        <v>https://leetcode.com/u/koushikraj17/</v>
       </c>
     </row>
     <row r="6">
